--- a/results/final/Italy_Results_v4.xlsx
+++ b/results/final/Italy_Results_v4.xlsx
@@ -1198,8 +1198,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100CBE255276945314790992D07276A2E9C" ma:contentTypeVersion="18" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="8675bac851cd0906af82d9b344b788d4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f58ec337-e214-4ba4-98b7-7d376ec9c384" xmlns:ns3="bce3f25c-6c94-415f-946f-6384d96b8749" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b0e9d441ae2c0b8244772fe863691a22" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100CBE255276945314790992D07276A2E9C" ma:contentTypeVersion="18" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e852c1eda4579854110eaa5540fcc087">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f58ec337-e214-4ba4-98b7-7d376ec9c384" xmlns:ns3="bce3f25c-6c94-415f-946f-6384d96b8749" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fcb9988e94d3ed424c91cebd889f8959" ns2:_="" ns3:_="">
     <xsd:import namespace="f58ec337-e214-4ba4-98b7-7d376ec9c384"/>
     <xsd:import namespace="bce3f25c-6c94-415f-946f-6384d96b8749"/>
     <xsd:element name="properties">
@@ -1473,7 +1473,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E6FDF3-1F0F-4910-86EB-BB10879FD72E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7A7FE3D-DAC5-4D0D-8951-2521F10A81FF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
